--- a/hmwebsite/modecraft/resources/data.xlsx
+++ b/hmwebsite/modecraft/resources/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\hmon.ir\hmwebsite\mode_practice\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\hmon.ir\hmwebsite\modecraft\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A0CAF0-5B23-4D95-BBBD-A990532C803B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B2126B-F1C1-4361-8BE3-C64E5E3120FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-315" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1064,7 +1064,9 @@
       <c r="B7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="6"/>
+      <c r="C7" s="6">
+        <v>8.5</v>
+      </c>
       <c r="D7" s="7" t="s">
         <v>17</v>
       </c>

--- a/hmwebsite/modecraft/resources/data.xlsx
+++ b/hmwebsite/modecraft/resources/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\hmon.ir\hmwebsite\modecraft\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B2126B-F1C1-4361-8BE3-C64E5E3120FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18FD58CA-3912-4F41-B5BF-0842E6C46646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-315" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1260,7 +1260,9 @@
       <c r="D21" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E21" s="8"/>
+      <c r="E21" s="8">
+        <v>110</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">

--- a/hmwebsite/modecraft/resources/data.xlsx
+++ b/hmwebsite/modecraft/resources/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\hmon.ir\hmwebsite\modecraft\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18FD58CA-3912-4F41-B5BF-0842E6C46646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8946F5-0167-4F33-98E8-340472474ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-315" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="76">
   <si>
     <t>A</t>
   </si>
@@ -51,9 +51,6 @@
     <t>QOZYjxy4JuI</t>
   </si>
   <si>
-    <t>Major</t>
-  </si>
-  <si>
     <t>Mixolydian</t>
   </si>
   <si>
@@ -63,9 +60,6 @@
     <t>Dorian</t>
   </si>
   <si>
-    <t>Minor</t>
-  </si>
-  <si>
     <t>Phrygian</t>
   </si>
   <si>
@@ -229,6 +223,36 @@
   </si>
   <si>
     <t>memgJJnBO4Q</t>
+  </si>
+  <si>
+    <t>F#</t>
+  </si>
+  <si>
+    <t>fHJCofxVWcA</t>
+  </si>
+  <si>
+    <t>xG48Ziz1IZk</t>
+  </si>
+  <si>
+    <t>HS1U1XTpSjY</t>
+  </si>
+  <si>
+    <t>Q0pOprPGb-Y</t>
+  </si>
+  <si>
+    <t>pjK05vL3eIM</t>
+  </si>
+  <si>
+    <t>ykNIq-xbS7c</t>
+  </si>
+  <si>
+    <t>4XSX5FaKvYc</t>
+  </si>
+  <si>
+    <t>Ionian</t>
+  </si>
+  <si>
+    <t>Aolian</t>
   </si>
 </sst>
 </file>
@@ -394,7 +418,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -408,6 +432,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -685,7 +715,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{60136BA0-8BE9-4FA7-B1EE-892539C320D9}" name="Table1" displayName="Table1" ref="A1:E50" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{60136BA0-8BE9-4FA7-B1EE-892539C320D9}" name="Table1" displayName="Table1" ref="A1:E57" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1AD5EB3C-54C0-4087-A62F-CCBCC37AB50C}" name="tonic" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{E199C3FD-3DC1-4BA8-996E-03DDA853F7D0}" name="mode" dataDxfId="3"/>
@@ -960,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -985,7 +1015,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -993,7 +1023,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="7" t="s">
@@ -1006,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="6">
         <v>2</v>
@@ -1021,7 +1051,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="7" t="s">
@@ -1036,11 +1066,11 @@
         <v>0</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E5" s="8"/>
     </row>
@@ -1049,11 +1079,11 @@
         <v>0</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E6" s="8"/>
     </row>
@@ -1062,13 +1092,13 @@
         <v>0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="6">
         <v>8.5</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" s="8"/>
     </row>
@@ -1077,188 +1107,188 @@
         <v>0</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E8" s="8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="6">
         <v>1.2</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C14" s="6">
         <v>21.5</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6">
         <v>22</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E17" s="8"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E18" s="8"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E19" s="8"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C20" s="6">
         <v>15</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E21" s="8">
         <v>110</v>
@@ -1266,193 +1296,193 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22" s="6">
         <v>56</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E22" s="8"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E23" s="8"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E24" s="8"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" s="6">
         <v>4</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E25" s="8"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E26" s="8"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E27" s="8"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E28" s="8"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E29" s="8"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E30" s="8"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" s="6">
         <v>36</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E31" s="8"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32" s="6">
         <v>0.7</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E32" s="8"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E33" s="8"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C34" s="6">
         <v>3</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E34" s="8"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E35" s="8">
         <v>100</v>
@@ -1460,180 +1490,180 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E36" s="8"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E37" s="8"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C38" s="6">
         <v>41</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E38" s="8"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E39" s="8"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E40" s="8"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C41" s="6"/>
       <c r="D41" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E41" s="8"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E42" s="8"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C43" s="6">
         <v>22</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E43" s="8"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E44" s="8"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C45" s="6">
         <v>12</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E45" s="8"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C46" s="6">
         <v>32</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E46" s="8"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="C47" s="6"/>
       <c r="D47" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E47" s="8"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C48" s="6">
         <v>21.5</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E48" s="8">
         <v>90</v>
@@ -1641,31 +1671,165 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C49" s="6">
         <v>19</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E49" s="8"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C50" s="10"/>
       <c r="D50" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E50" s="12"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C51" s="6"/>
+      <c r="D51" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E51" s="8"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="6"/>
+      <c r="D52" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E52" s="8">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="6"/>
+      <c r="D53" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E53" s="8"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C54" s="6"/>
+      <c r="D54" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E54" s="8"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="6"/>
+      <c r="D55" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="8"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" s="6">
+        <v>7</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E56" s="8"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="6">
+        <v>4</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" s="8"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="13"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="15"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="13"/>
+      <c r="D59" s="14"/>
+      <c r="E59" s="15"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="13"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="15"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="13"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="15"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="13"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="15"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="13"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="15"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="13"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="16"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
